--- a/artfynd/A 27199-2025 artfynd.xlsx
+++ b/artfynd/A 27199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095925</v>
       </c>
       <c r="B2" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130095936</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>130095920</v>
       </c>
       <c r="B4" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130095927</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27199-2025 artfynd.xlsx
+++ b/artfynd/A 27199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095925</v>
       </c>
       <c r="B2" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130095936</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>130095920</v>
       </c>
       <c r="B4" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130095927</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27199-2025 artfynd.xlsx
+++ b/artfynd/A 27199-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130095925</v>
       </c>
       <c r="B2" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130095936</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>130095920</v>
       </c>
       <c r="B4" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130095927</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27199-2025 artfynd.xlsx
+++ b/artfynd/A 27199-2025 artfynd.xlsx
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130095925</v>
+        <v>130095920</v>
       </c>
       <c r="B2" t="n">
-        <v>97797</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602684</v>
+        <v>602879</v>
       </c>
       <c r="R2" t="n">
-        <v>6750951</v>
+        <v>6751102</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130095936</v>
+        <v>130095927</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>148</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602887</v>
+        <v>602871</v>
       </c>
       <c r="R3" t="n">
-        <v>6751109</v>
+        <v>6751104</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130095920</v>
+        <v>130095925</v>
       </c>
       <c r="B4" t="n">
-        <v>93013</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,26 +915,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602879</v>
+        <v>602684</v>
       </c>
       <c r="R4" t="n">
-        <v>6751102</v>
+        <v>6750951</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130095927</v>
+        <v>130095936</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602871</v>
+        <v>602887</v>
       </c>
       <c r="R5" t="n">
-        <v>6751104</v>
+        <v>6751109</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
